--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Mistral-Small-3.2-24B-Instruct-2506/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Mistral-Small-3.2-24B-Instruct-2506/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,7 +450,7 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>355</v>
@@ -459,7 +459,7 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H3">
         <v>426</v>
